--- a/data/credit_bond_2026-07-23.xlsx
+++ b/data/credit_bond_2026-07-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-23" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-24" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,6 +37,10 @@
       <sz val="12.0"/>
       <color indexed="8"/>
       <b val="true"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="12.0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -90,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
@@ -99,6 +103,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
       <alignment horizontal="center" wrapText="true" vertical="center"/>
       <protection locked="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyBorder="true" applyFont="true">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
 </styleSheet>
@@ -149,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -163,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-23</t>
+          <t>数据来源：DM    2026-07-24</t>
         </is>
       </c>
     </row>
@@ -667,6 +677,884 @@
         <is>
           <t>团费(%)</t>
         </is>
+      </c>
+    </row>
+    <row r="3" customHeight="true" ht="18.0">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01B</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>1.35 ~ 1.85</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>1.5900/--</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种二)</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY3" s="3"/>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26长开G1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>07-23 19:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>245671.SH</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>24长寿开投MTN003A</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1.10Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>1.7196</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>1.7300/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>07-23 15:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>a-</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>重庆市-长寿区</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还回售的公司债券本金[23长开04]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>重庆长寿开发投资(集团)有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2027-07-28</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26恒丰银行绿债01A</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>25恒丰银行债02</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>1.83Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1.5832</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>1.5900/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目。</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,国泰海通证券股份有限公司,东方证券股份有限公司,申万宏源证券有限公司,德邦证券股份有限公司,中国进出口银行,中国银行股份有限公司,中国建设银行股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>恒丰银行股份有限公司2026年第一期绿色金融债券(品种一)</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-27</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>股份制银行</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26成都开投PPN001</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>07-23 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5+5</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25成都开投PPN002</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>4.31Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2.1942</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>07-23 09:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>2.21%~2.31%</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>四川省-成都市</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>本次定向债务融资工具注册金额为20亿元,本期发行金额为13亿元,募集资金均用于偿还发行人存量债务融资工具本金；本期募集资金13亿元用于置换上述银行贷款本金[23成都国投PPN001]</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>广发证券股份有限公司,成都银行股份有限公司,国投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>成都经开国投集团有限公司2026年度第一期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2036-07-24</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-24</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AY6" s="4" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/data/credit_bond_2026-07-23.xlsx
+++ b/data/credit_bond_2026-07-23.xlsx
@@ -1366,8 +1366,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>51.75</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -1413,7 +1417,9 @@
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="4" t="n">
+        <v>3.58</v>
+      </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-07-23.xlsx
+++ b/data/credit_bond_2026-07-23.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>07-27 18:00</t>
+          <t>07-27 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.2952</t>
+          <t>2.2945</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">

--- a/data/credit_bond_2026-07-23.xlsx
+++ b/data/credit_bond_2026-07-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-27</t>
+          <t>数据来源：DM    2026-07-28</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,9 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.34</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_2026-07-23.xlsx
+++ b/data/credit_bond_2026-07-23.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-07-28" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-07-29" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -173,252 +173,252 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-07-28</t>
+          <t>数据来源：DM    2026-07-29</t>
         </is>
       </c>
     </row>
@@ -682,55 +682,57 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26鸿飞02</t>
+          <t>26滨江投资PPN002</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>07-27 19:00</t>
+          <t>07-27 18:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>283448.SH</t>
+          <t>032680420.IB</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>8.8</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>8.8</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>26鸿飞01</t>
+          <t>25滨江投资PPN009</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.67Y</t>
+          <t>2.22Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.2945</t>
+          <t>1.7061</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -740,17 +742,17 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司</t>
+          <t>南京滨江投资发展有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>07-27 15:00</t>
+          <t>07-24 09:00</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
@@ -758,52 +760,52 @@
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
+      <c r="S3" s="4" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>2.56</v>
+      </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
-          <t>a+</t>
+          <t>a</t>
         </is>
       </c>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>2.03%~2.13%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>四川省-绵阳市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券23江油02的本金[23江油02]</t>
+          <t>本期定向债务融资工具发行金额8.8亿元,将全部用于偿还发行人有息债务[26滨江投资PPN001,21滨江投资PPN005]</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>四川省金玉融资担保有限公司</t>
-        </is>
-      </c>
+          <t>杭州银行股份有限公司,宁波银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC3" s="3"/>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr">
@@ -813,12 +815,12 @@
       </c>
       <c r="AF3" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AG3" s="3" t="inlineStr">
         <is>
-          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>南京滨江投资发展有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AH3" s="3" t="inlineStr">
@@ -828,81 +830,2301 @@
       </c>
       <c r="AI3" s="3" t="inlineStr">
         <is>
-          <t>2031-07-28</t>
+          <t>2028-07-28</t>
         </is>
       </c>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3" t="inlineStr">
         <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AL3" s="3" t="inlineStr">
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AY3" s="4" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" customHeight="true" ht="18.0">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>26景国资PPN001A</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>07-27 18:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>032601644.IB</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>24景国资PPN003</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>3.00Y</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>2.0500</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>景德镇市国资运营投资控股集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>07-27 10:00</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>a-</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>2.03%~2.13%</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>江西省-景德镇市</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>本次定向债务融资工具本期发行规模5亿元,拟全部用于归还发行人存量债务融资工具[25景国资CP002]</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>光大证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>景德镇市国资运营投资控股集团有限责任公司2026年度第一期定向债务融资工具(品种一)</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3"/>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>橡胶</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-28</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AY4" s="3"/>
+    </row>
+    <row r="5" customHeight="true" ht="18.0">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>26衡阳城投PPN004</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>07-27 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>032601651.IB</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>5+2+2+1</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>26衡阳城投PPN003</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>4.97Y+5.00Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>2.0785</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>2.0900/2.0800</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>衡阳市城市建设投资有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>07-27 14:00</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>2.00%~2.10%</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-衡阳市</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>本期发行金额上限为3亿元,募集资金用于偿还发行人存续债务融资工具[23衡阳城投MTN004]</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>衡阳市城市建设投资有限公司2026年度第四期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>2036-07-28</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AY5" s="3"/>
+    </row>
+    <row r="6" customHeight="true" ht="18.0">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>26景国资PPN001B</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>07-27 18:00</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>032601645.IB</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25景德3A</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>4.22Y</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2.2483</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>2.2500/2.2300</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>景德镇市国资运营投资控股集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>07-27 10:00</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>a-</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>2.29%~2.39%</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>江西省-景德镇市</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>本次定向债务融资工具本期发行规模5亿元,拟全部用于归还发行人存量债务融资工具[25景国资CP002]</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>光大证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>景德镇市国资运营投资控股集团有限责任公司2026年度第一期定向债务融资工具(品种二)</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>橡胶</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AY6" s="3"/>
+    </row>
+    <row r="7" customHeight="true" ht="18.0">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>26鸿飞02</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>07-27 19:00</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>283448.SH</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>26鸿飞01</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>4.67Y</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2.2945</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>江油鸿飞投资(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>07-27 15:00</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>a+</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>2.03%~2.13%</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>四川省-绵阳市</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>本次公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券23江油02的本金[23江油02]</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>长城证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>四川省金玉融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>江油鸿飞投资(集团)有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-28</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
+      <c r="AM7" s="3" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
+      <c r="AN7" s="3" t="inlineStr">
         <is>
           <t>城投</t>
         </is>
       </c>
-      <c r="AO3" s="3" t="inlineStr">
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AQ3" s="3" t="inlineStr">
+      <c r="AQ7" s="3" t="inlineStr">
         <is>
           <t>国资经营</t>
         </is>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
+      <c r="AR7" s="3" t="inlineStr">
         <is>
           <t>国资经营</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="AU3" s="3" t="inlineStr">
+      <c r="AU7" s="3" t="inlineStr">
         <is>
           <t>有担保</t>
         </is>
       </c>
-      <c r="AV3" s="3" t="inlineStr">
+      <c r="AV7" s="3" t="inlineStr">
         <is>
           <t>不含权</t>
         </is>
       </c>
-      <c r="AW3" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="AY3" s="3"/>
+      <c r="AY7" s="3"/>
+    </row>
+    <row r="8" customHeight="true" ht="18.0">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>26株洲城建MTN002A</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>07-28 18:00</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>102682805.IB</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>24株洲城建MTN003</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>2.93Y</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>1.7693</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>1.8000/--</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>株洲市城市建设发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>07-28 09:00</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-株洲市</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据基础发行规模0亿元,发行金额上限6亿元,募集资金用于偿还发行人本部债务融资工具本金[25株洲城建MTN001]</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期中期票据(品种一)</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-29</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AY8" s="3"/>
+    </row>
+    <row r="9" customHeight="true" ht="18.0">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>26滨江投资PPN003</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>07-28 18:00</t>
+        </is>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>25滨江投资PPN009</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2.21Y</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>1.7109</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>南京滨江投资发展有限公司</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>07-28 09:00</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-南京市</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>本期定向债务融资工具发行金额4.6亿元,将全部用于偿还发行人有息债务[25滨江投资PPN008]</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>中国民生银行股份有限公司,西部证券股份有限公司,中信银行股份有限公司,江苏江南农村商业银行股份有限公司,兴业银行股份有限公司,杭州银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>南京滨江投资发展有限公司2026年度第三期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>2028-07-29</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AY9" s="4" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10" customHeight="true" ht="18.0">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>26株洲城建MTN002B</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>07-28 18:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102682806.IB</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>25株发01</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>4.12Y</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>2.0239</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>株洲市城市建设发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>07-28 09:00</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>1.92%~2.02%</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-株洲市</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据基础发行规模0亿元,发行金额上限6亿元,募集资金用于偿还发行人本部债务融资工具本金[25株洲城建MTN001]</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>兴业银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>中期票据</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>株洲市城市建设发展集团有限公司2026年度第二期中期票据(品种二)</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>2031-07-29</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AY10" s="3"/>
+    </row>
+    <row r="11" customHeight="true" ht="18.0">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>26三江Y1</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>07-28 19:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>520339.SZ</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>3+N</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>24三江02</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>2.75Y</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>1.8230</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>宜宾三江投资建设集团有限公司</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>07-28 15:00</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>四川省-宜宾市</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还有息负债</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司,广发证券股份有限公司,天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>宜宾三江投资建设集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-30</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>综合基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>永续</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AY11" s="3"/>
+    </row>
+    <row r="12" customHeight="true" ht="18.0">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>26湖南银行债01</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>07-29 16:30</t>
+        </is>
+      </c>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>25湖南银行债01</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>2.02Y</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>1.5812</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>湖南银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>07-29 09:00</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-长沙市</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。 </t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,东方证券股份有限公司,中国银行股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>商业银行普通债券</t>
+        </is>
+      </c>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>湖南银行股份有限公司2026年第一期金融债券</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-31</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>城商行</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AY12" s="3"/>
+    </row>
+    <row r="13" customHeight="true" ht="18.0">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>26舟城F2</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>07-29 18:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>283481.SH</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>25舟城F2</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>2.15Y</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>1.7193</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>舟山海城建设投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>07-29 15:00</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>aa序列</t>
+        </is>
+      </c>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-舟山市</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金拟全部用于偿还到期的公司债券本金[23舟城F3]</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>舟山海城建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>2029-07-31</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AY13" s="3"/>
     </row>
   </sheetData>
   <mergeCells>
